--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/NORTH_CAROLINA_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/NORTH_CAROLINA_2010.xlsx
@@ -2670,7 +2670,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C129">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C188">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C218">
@@ -13902,7 +13902,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C753">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C842">
@@ -15522,7 +15522,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C843">
@@ -15990,7 +15990,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C869">
@@ -16098,7 +16098,7 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C875">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1246">
@@ -25998,7 +25998,7 @@
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1425">
